--- a/docs/data/jp/xlsx/5992.xlsx
+++ b/docs/data/jp/xlsx/5992.xlsx
@@ -7360,7 +7360,7 @@
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>Cost For Quality Guarantee NOE</t>
+          <t>품질보증 비용</t>
         </is>
       </c>
       <c r="D102" s="20" t="n">
@@ -7702,7 +7702,7 @@
     <row r="111">
       <c r="A111" s="18" t="inlineStr">
         <is>
-          <t>Loss On Accident Of Fujioka4th Plant EL</t>
+          <t>후지오카 제4공장 사고 관련 손실</t>
         </is>
       </c>
       <c r="E111" s="20" t="n">
@@ -10388,7 +10388,7 @@
     <row r="163">
       <c r="A163" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Loss On Disaster Ope CF</t>
+          <t>재해손실 충당금 증감액</t>
         </is>
       </c>
       <c r="E163" s="20" t="n">
@@ -10419,7 +10419,7 @@
     <row r="164">
       <c r="A164" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Business Structure Improvement Ope CF</t>
+          <t>사업구조개선 충당금 증감액</t>
         </is>
       </c>
       <c r="E164" s="20" t="n">
@@ -11987,7 +11987,7 @@
     <row r="199">
       <c r="A199" s="18" t="inlineStr">
         <is>
-          <t>Collection Of Long Term Prepaid Expenses Inv CF</t>
+          <t>장기선급비용 회수 수입</t>
         </is>
       </c>
       <c r="E199" s="20" t="n">
@@ -17374,7 +17374,7 @@
     <row r="116">
       <c r="A116" s="18" t="inlineStr">
         <is>
-          <t>Provision For Loss On Disaster CL</t>
+          <t>재해손실 충당금</t>
         </is>
       </c>
       <c r="C116" s="20" t="n">
@@ -17402,7 +17402,7 @@
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
-          <t>Provision For Business Structure Improvement CL</t>
+          <t>사업구조개선 충당금</t>
         </is>
       </c>
       <c r="C117" s="20" t="n">
